--- a/data/season2026/tpbl_summary.xlsx
+++ b/data/season2026/tpbl_summary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\script\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frank.wong\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58300832-E13D-4226-A7F4-B376E757E330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58682A9E-D9EE-4A47-A79F-9573D992439C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="7隊戰力與綜合評分" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="95">
   <si>
     <t>2026-2027 賽季 TPBL 例行賽 7隊戰力與綜合評分總表 (截至 2026.10.25 完賽)</t>
   </si>
@@ -74,108 +74,108 @@
     <t>福爾摩沙夢想家</t>
   </si>
   <si>
-    <t>2場</t>
+    <t>1勝-1敗</t>
+  </si>
+  <si>
+    <t>42.1%</t>
+  </si>
+  <si>
+    <t>38.3%</t>
+  </si>
+  <si>
+    <t>47.8%</t>
+  </si>
+  <si>
+    <t>15.7%</t>
+  </si>
+  <si>
+    <t>新北國王</t>
+  </si>
+  <si>
+    <t>2勝-0敗</t>
+  </si>
+  <si>
+    <t>40.0%</t>
+  </si>
+  <si>
+    <t>31.9%</t>
+  </si>
+  <si>
+    <t>45.6%</t>
+  </si>
+  <si>
+    <t>18.0%</t>
+  </si>
+  <si>
+    <t>高雄全家海神</t>
+  </si>
+  <si>
+    <t>49.8%</t>
+  </si>
+  <si>
+    <t>49.0%</t>
+  </si>
+  <si>
+    <t>20.2%</t>
+  </si>
+  <si>
+    <t>新北中信特攻</t>
+  </si>
+  <si>
+    <t>0勝-1敗</t>
+  </si>
+  <si>
+    <t>33.3%</t>
+  </si>
+  <si>
+    <t>50.0%</t>
+  </si>
+  <si>
+    <t>41.1%</t>
+  </si>
+  <si>
+    <t>18.4%</t>
+  </si>
+  <si>
+    <t>臺北台新戰神</t>
+  </si>
+  <si>
+    <t>桃園台啤永豐雲豹</t>
+  </si>
+  <si>
+    <t>新竹御嵿攻城獅</t>
+  </si>
+  <si>
+    <t>41.9%</t>
+  </si>
+  <si>
+    <t>26.5%</t>
+  </si>
+  <si>
+    <t>46.2%</t>
+  </si>
+  <si>
+    <t>15.0%</t>
+  </si>
+  <si>
+    <t>【區塊 B：重點球員洞察與戰力短評 (Player Insights &amp; Team Evaluation)】</t>
+  </si>
+  <si>
+    <t>開季戰績</t>
+  </si>
+  <si>
+    <t>高球權核心 (USG% &gt; 25% 且 TS% &gt; 55%)</t>
+  </si>
+  <si>
+    <t>高效終結者 (GmSc 前二且 eFG% &gt; 60%)</t>
+  </si>
+  <si>
+    <t>戰力短評與攻防體系洞察</t>
   </si>
   <si>
     <t>1勝1敗</t>
   </si>
   <si>
-    <t>新北國王</t>
-  </si>
-  <si>
-    <t>2勝-0敗</t>
-  </si>
-  <si>
-    <t>18.3%</t>
-  </si>
-  <si>
-    <t>14.5%</t>
-  </si>
-  <si>
-    <t>21.5%</t>
-  </si>
-  <si>
-    <t>9.3%</t>
-  </si>
-  <si>
-    <t>高雄全家海神</t>
-  </si>
-  <si>
-    <t>1勝-1敗</t>
-  </si>
-  <si>
-    <t>20.7%</t>
-  </si>
-  <si>
-    <t>24.9%</t>
-  </si>
-  <si>
-    <t>25.9%</t>
-  </si>
-  <si>
-    <t>11.8%</t>
-  </si>
-  <si>
-    <t>新北中信特攻</t>
-  </si>
-  <si>
-    <t>0勝-1敗</t>
-  </si>
-  <si>
-    <t>33.3%</t>
-  </si>
-  <si>
-    <t>50.0%</t>
-  </si>
-  <si>
-    <t>41.1%</t>
-  </si>
-  <si>
-    <t>18.4%</t>
-  </si>
-  <si>
-    <t>臺北台新戰神</t>
-  </si>
-  <si>
-    <t>0場</t>
-  </si>
-  <si>
-    <t>0勝0敗</t>
-  </si>
-  <si>
-    <t>桃園台啤永豐雲豹</t>
-  </si>
-  <si>
-    <t>新竹御嵿攻城獅</t>
-  </si>
-  <si>
-    <t>41.9%</t>
-  </si>
-  <si>
-    <t>26.5%</t>
-  </si>
-  <si>
-    <t>46.2%</t>
-  </si>
-  <si>
-    <t>15.0%</t>
-  </si>
-  <si>
-    <t>【區塊 B：重點球員洞察與戰力短評 (Player Insights &amp; Team Evaluation)】</t>
-  </si>
-  <si>
-    <t>開季戰績</t>
-  </si>
-  <si>
-    <t>高球權核心 (USG% &gt; 25% 且 TS% &gt; 55%)</t>
-  </si>
-  <si>
-    <t>高效終結者 (GmSc 前二且 eFG% &gt; 60%)</t>
-  </si>
-  <si>
-    <t>戰力短評與攻防體系洞察</t>
-  </si>
-  <si>
     <t>林俊吉 (USG% 30.9%, TS% 57.3%)、基德 (USG% 25.1%, TS% 55.6%)</t>
   </si>
   <si>
@@ -185,9 +185,39 @@
     <t>百回合進攻效率達 100.5 且次戰失誤率顯著降至 11.0%，本土雙衛與高柏鎧護框展現極高容錯率與逆轉韌性。</t>
   </si>
   <si>
+    <t>2勝0敗</t>
+  </si>
+  <si>
+    <t>克雷格 (USG% 27.7%, TS% 59.5%)、林書緯 (USG% 25.4%, TS% 57.8%)</t>
+  </si>
+  <si>
+    <t>熊祥泰 (GmSc 7.2, eFG% 78.6%)、李愷諺 (GmSc 11.7, eFG% 57.1% / TS% 63.2%) [註：雙主力沃許本場均 GmSc 10.0/eFG% 50.0%、肯刀爾場均 GmSc 13.9/eFG% 34.3% 產量居內線前列，因外線與終結分佈致 eFG% 未達 60% 門檻]</t>
+  </si>
+  <si>
+    <t>開季斬獲二連勝，在次戰肯刀爾與克雷格手感欠佳之際，林書緯挺身而出飆進 4 記三分貢獻 18 分 6 助攻（正負值 +20），沃許本下半場禁區攻守兼備（17分9板3阻攻）；團隊二陣輪替與本土抗壓性極佳，下半場打出 47:33 攻勢完成逆轉。</t>
+  </si>
+  <si>
+    <t>貝西里 (USG% 29.0%, TS% 59.2%)、洛斯柯 (USG% 36.3%, TS% 57.4%)</t>
+  </si>
+  <si>
+    <t>呂威霆 (場均 GmSc 0.9, eFG% 62.5%) [註：雙主力貝西里場均 GmSc 26.3/eFG% 57.0%、洛斯柯場均 GmSc 24.3/eFG% 45.7% 產量居全隊前二，因高罰球比重致使 eFG% 未達 60% 門檻]</t>
+  </si>
+  <si>
+    <t>雙延長賽中展現出色的進攻侵略性，洛斯柯單場製造 30 次罰球狂砍 42 分 22 籃板；本土側翼胡瓏貿與施晉堯替補上陣提供防守硬度，蘇文儒外線挹注關鍵火力，成功在高速攻防（兩戰平均 Pace 達 119.7）中收下賽季首勝。</t>
+  </si>
+  <si>
     <t>0勝1敗</t>
   </si>
   <si>
+    <t>法拉帝 (USG% 29.3%, TS% 61.2%)</t>
+  </si>
+  <si>
+    <t>謝亞軒 (GmSc 12.6, eFG% 61.1%)、法拉帝 (GmSc 16.0, eFG% 58.3% / TS% 61.2%)</t>
+  </si>
+  <si>
+    <t>開季首戰展現歐陸傳導體系優勢，首節外線狂轟 7 記三分建立雙位數領先；法拉帝內線攻下 19 分 15 籃板發揮穩定。然而下半場進攻嚴重斷線，洋將猛士手感低迷（21投3中、三分9投0中），加上全隊送出 17 次失誤，陣地戰缺乏第二單打終結點遭國王翻盤。</t>
+  </si>
+  <si>
     <t>尚未出賽</t>
   </si>
   <si>
@@ -195,6 +225,15 @@
   </si>
   <si>
     <t>截至10/18尚未出賽，已完成完整球員名單與數據架構建置，待後續賽程展開即時納入。</t>
+  </si>
+  <si>
+    <t>迪亞洛 (USG% 32.2%, TS% 71.4%)</t>
+  </si>
+  <si>
+    <t>迪亞洛 (GmSc 39.8, eFG% 73.9%)、德魯 (GmSc 27.8, eFG% 76.9%)</t>
+  </si>
+  <si>
+    <t>首戰即與對手鏖戰至雙延長賽，先發雙洋將展現強大統治力——迪亞洛禁區強攻 41 分 19 板、德魯繳出 23 分 12 板 8 助 5 阻攻準大三元；本土新秀劉丞勳出戰近 52 分鐘正負值達 +9。球隊隱憂在於板凳後場手感冰冷（陳力生 14 投 0 中）與全隊罰球失準（團隊罰球率僅 56.8%），成為首戰惜敗關鍵。</t>
   </si>
   <si>
     <t>2026-2027 賽季 TPBL 例行賽主力球員：球權使用率 (USG%) vs 真實命中率 (TS%) 核心效率對比與象限深度解讀</t>
@@ -275,53 +314,44 @@
     <t>肯刀爾狂轟33分造13罰展現破壞力但外線4中0且出手25次；加爾文攻下16分11板但出現6次失誤；馬建豪兩戰場均17分外線量大需維持穩定度。</t>
   </si>
   <si>
-    <t>1場</t>
-  </si>
-  <si>
-    <t>貝西里 (USG% 29.0%, TS% 59.2%)、洛斯柯 (USG% 36.3%, TS% 57.4%)</t>
-  </si>
-  <si>
-    <t>呂威霆 (場均 GmSc 0.9, eFG% 62.5%) [註：雙主力貝西里場均 GmSc 26.3/eFG% 57.0%、洛斯柯場均 GmSc 24.3/eFG% 45.7% 產量居全隊前二，因高罰球比重致使 eFG% 未達 60% 門檻]</t>
-  </si>
-  <si>
-    <t>雙延長賽中展現出色的進攻侵略性，洛斯柯單場製造 30 次罰球狂砍 42 分 22 籃板；本土側翼胡瓏貿與施晉堯替補上陣提供防守硬度，蘇文儒外線挹注關鍵火力，成功在高速攻防（兩戰平均 Pace 達 119.7）中收下賽季首勝。</t>
-  </si>
-  <si>
-    <t>迪亞洛 (USG% 32.2%, TS% 71.4%)</t>
-  </si>
-  <si>
-    <t>迪亞洛 (GmSc 39.8, eFG% 73.9%)、德魯 (GmSc 27.8, eFG% 76.9%)</t>
-  </si>
-  <si>
-    <t>首戰即與對手鏖戰至雙延長賽，先發雙洋將展現強大統治力——迪亞洛禁區強攻 41 分 19 板、德魯繳出 23 分 12 板 8 助 5 阻攻準大三元；本土新秀劉丞勳出戰近 52 分鐘正負值達 +9。球隊隱憂在於板凳後場手感冰冷（陳力生 14 投 0 中）與全隊罰球失準（團隊罰球率僅 56.8%），成為首戰惜敗關鍵。</t>
-  </si>
-  <si>
-    <t>克雷格 (USG% 27.7%, TS% 59.5%)、林書緯 (USG% 25.4%, TS% 57.8%)</t>
-  </si>
-  <si>
-    <t>熊祥泰 (GmSc 7.2, eFG% 78.6%)、李愷諺 (GmSc 11.7, eFG% 57.1% / TS% 63.2%) [註：雙主力沃許本場均 GmSc 10.0/eFG% 50.0%、肯刀爾場均 GmSc 13.9/eFG% 34.3% 產量居內線前列，因外線與終結分佈致 eFG% 未達 60% 門檻]</t>
-  </si>
-  <si>
-    <t>開季斬獲二連勝，在次戰肯刀爾與克雷格手感欠佳之際，林書緯挺身而出飆進 4 記三分貢獻 18 分 6 助攻（正負值 +20），沃許本下半場禁區攻守兼備（17分9板3阻攻）；團隊二陣輪替與本土抗壓性極佳，下半場打出 47:33 攻勢完成逆轉。</t>
-  </si>
-  <si>
-    <t>2勝0敗</t>
-  </si>
-  <si>
-    <t>法拉帝 (USG% 29.3%, TS% 61.2%)</t>
-  </si>
-  <si>
-    <t>謝亞軒 (GmSc 12.6, eFG% 61.1%)、法拉帝 (GmSc 16.0, eFG% 58.3% / TS% 61.2%)</t>
-  </si>
-  <si>
-    <t>開季首戰展現歐陸傳導體系優勢，首節外線狂轟 7 記三分建立雙位數領先；法拉帝內線攻下 19 分 15 籃板發揮穩定。然而下半場進攻嚴重斷線，洋將猛士手感低迷（21投3中、三分9投0中），加上全隊送出 17 次失誤，陣地戰缺乏第二單打終結點遭國王翻盤。</t>
+    <r>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF181C1F"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>勝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF181C1F"/>
+        <rFont val="Roboto"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF181C1F"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>敗</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -379,6 +409,20 @@
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF181C1F"/>
+      <name val="細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="5">
@@ -505,10 +549,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -516,22 +560,18 @@
   <dxfs count="5">
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
         <color rgb="FF181C1F"/>
         <name val="Roboto"/>
-        <scheme val="none"/>
       </font>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="right" vertical="bottom"/>
+      <border>
         <left style="thin">
           <color rgb="FF73777E"/>
         </left>
@@ -838,23 +878,23 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:M22"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="27.6640625" customWidth="1"/>
-    <col min="2" max="2" width="7.6640625" customWidth="1"/>
-    <col min="3" max="4" width="37.6640625" customWidth="1"/>
-    <col min="5" max="5" width="45.88671875" customWidth="1"/>
-    <col min="6" max="6" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="27.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.21875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="24.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.33203125" customWidth="1"/>
-    <col min="12" max="12" width="18.88671875" customWidth="1"/>
-    <col min="13" max="13" width="21.21875" customWidth="1"/>
+    <col min="1" max="1" width="27.7109375" customWidth="1"/>
+    <col min="2" max="2" width="7.7109375" customWidth="1"/>
+    <col min="3" max="4" width="37.7109375" customWidth="1"/>
+    <col min="5" max="5" width="45.85546875" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.28515625" customWidth="1"/>
+    <col min="12" max="12" width="18.85546875" customWidth="1"/>
+    <col min="13" max="13" width="21.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -871,7 +911,7 @@
       <c r="L1" s="5"/>
       <c r="M1" s="5"/>
     </row>
-    <row r="2" spans="1:13" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
@@ -888,25 +928,25 @@
       <c r="L2" s="7"/>
       <c r="M2" s="7"/>
     </row>
-    <row r="3" spans="1:13" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="15" t="s">
+    <row r="3" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="16"/>
-      <c r="L4" s="16"/>
-      <c r="M4" s="17"/>
-    </row>
-    <row r="5" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="18"/>
+    </row>
+    <row r="5" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>3</v>
       </c>
@@ -947,59 +987,59 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="10">
+        <v>2</v>
+      </c>
+      <c r="C6" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="10" t="s">
-        <v>18</v>
-      </c>
       <c r="D6" s="11">
-        <v>505</v>
+        <v>480</v>
       </c>
       <c r="E6" s="11">
         <v>221</v>
       </c>
       <c r="F6" s="11">
-        <v>182</v>
-      </c>
-      <c r="G6" s="12">
-        <v>0.42299999999999999</v>
-      </c>
-      <c r="H6" s="12">
-        <v>0.379</v>
-      </c>
-      <c r="I6" s="12">
-        <v>0.48099999999999998</v>
+        <v>183</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>20</v>
       </c>
       <c r="J6" s="11">
-        <v>219.8</v>
+        <v>223.8</v>
       </c>
       <c r="K6" s="11">
-        <v>104.5</v>
+        <v>111.9</v>
       </c>
       <c r="L6" s="11">
-        <v>100.5</v>
-      </c>
-      <c r="M6" s="12">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="13.2" x14ac:dyDescent="0.25">
+        <v>98.7</v>
+      </c>
+      <c r="M6" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>17</v>
+        <v>22</v>
+      </c>
+      <c r="B7" s="10">
+        <v>2</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D7" s="11">
-        <v>505</v>
+        <v>480</v>
       </c>
       <c r="E7" s="11">
         <v>202</v>
@@ -1008,36 +1048,36 @@
         <v>160</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J7" s="11">
         <v>205.5</v>
       </c>
       <c r="K7" s="11">
-        <v>97.7</v>
+        <v>102.8</v>
       </c>
       <c r="L7" s="11">
         <v>98.3</v>
       </c>
       <c r="M7" s="12" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="13.2" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="10">
+        <v>2</v>
+      </c>
+      <c r="C8" s="10" t="s">
         <v>17</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>26</v>
       </c>
       <c r="D8" s="11">
         <v>480</v>
@@ -1049,36 +1089,36 @@
         <v>195</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J8" s="11">
-        <v>239.5</v>
+        <v>237.5</v>
       </c>
       <c r="K8" s="11">
-        <v>119.7</v>
+        <v>118.7</v>
       </c>
       <c r="L8" s="11">
-        <v>102.7</v>
+        <v>103.6</v>
       </c>
       <c r="M8" s="12" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="13.2" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>81</v>
+        <v>32</v>
+      </c>
+      <c r="B9" s="10">
+        <v>1</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D9" s="11">
         <v>240</v>
@@ -1090,13 +1130,13 @@
         <v>90</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J9" s="11">
         <v>92.4</v>
@@ -1108,100 +1148,100 @@
         <v>87.7</v>
       </c>
       <c r="M9" s="12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="13.2" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" s="10" t="s">
         <v>38</v>
       </c>
+      <c r="B10" s="10">
+        <v>0</v>
+      </c>
       <c r="C10" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="D10" s="11">
+        <v>0</v>
+      </c>
+      <c r="E10" s="11">
+        <v>0</v>
+      </c>
+      <c r="F10" s="11">
+        <v>0</v>
+      </c>
+      <c r="G10" s="11">
+        <v>0</v>
+      </c>
+      <c r="H10" s="11">
+        <v>0</v>
+      </c>
+      <c r="I10" s="11">
+        <v>0</v>
+      </c>
+      <c r="J10" s="11">
+        <v>0</v>
+      </c>
+      <c r="K10" s="11">
+        <v>0</v>
+      </c>
+      <c r="L10" s="11">
+        <v>0</v>
+      </c>
+      <c r="M10" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="11">
-        <v>0</v>
-      </c>
-      <c r="E10" s="11">
-        <v>0</v>
-      </c>
-      <c r="F10" s="11">
-        <v>0</v>
-      </c>
-      <c r="G10" s="12">
-        <v>0</v>
-      </c>
-      <c r="H10" s="12">
-        <v>0</v>
-      </c>
-      <c r="I10" s="12">
-        <v>0</v>
-      </c>
-      <c r="J10" s="11">
-        <v>0</v>
-      </c>
-      <c r="K10" s="11">
-        <v>0</v>
-      </c>
-      <c r="L10" s="11">
-        <v>0</v>
-      </c>
-      <c r="M10" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
+      <c r="B11" s="10">
+        <v>0</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="D11" s="11">
+        <v>0</v>
+      </c>
+      <c r="E11" s="11">
+        <v>0</v>
+      </c>
+      <c r="F11" s="11">
+        <v>0</v>
+      </c>
+      <c r="G11" s="11">
+        <v>0</v>
+      </c>
+      <c r="H11" s="11">
+        <v>0</v>
+      </c>
+      <c r="I11" s="11">
+        <v>0</v>
+      </c>
+      <c r="J11" s="11">
+        <v>0</v>
+      </c>
+      <c r="K11" s="11">
+        <v>0</v>
+      </c>
+      <c r="L11" s="11">
+        <v>0</v>
+      </c>
+      <c r="M11" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" s="11">
-        <v>0</v>
-      </c>
-      <c r="E11" s="11">
-        <v>0</v>
-      </c>
-      <c r="F11" s="11">
-        <v>0</v>
-      </c>
-      <c r="G11" s="12">
-        <v>0</v>
-      </c>
-      <c r="H11" s="12">
-        <v>0</v>
-      </c>
-      <c r="I11" s="12">
-        <v>0</v>
-      </c>
-      <c r="J11" s="11">
-        <v>0</v>
-      </c>
-      <c r="K11" s="11">
-        <v>0</v>
-      </c>
-      <c r="L11" s="11">
-        <v>0</v>
-      </c>
-      <c r="M11" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>81</v>
+      <c r="B12" s="10">
+        <v>1</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D12" s="11">
         <v>240</v>
@@ -1213,13 +1253,13 @@
         <v>117</v>
       </c>
       <c r="G12" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="H12" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="H12" s="12" t="s">
+      <c r="I12" s="12" t="s">
         <v>43</v>
-      </c>
-      <c r="I12" s="12" t="s">
-        <v>44</v>
       </c>
       <c r="J12" s="11">
         <v>126.3</v>
@@ -1231,42 +1271,42 @@
         <v>102.2</v>
       </c>
       <c r="M12" s="12" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="16" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="17"/>
-    </row>
-    <row r="15" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="18"/>
+    </row>
+    <row r="15" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B15" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="D15" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="E15" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="E15" s="13" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="39.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>16</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="C16" s="14" t="s">
         <v>51</v>
@@ -1278,106 +1318,106 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="92.4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" ht="76.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>91</v>
+        <v>22</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>54</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>88</v>
+        <v>55</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="66" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="10" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="79.2" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="B19" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="C19" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>93</v>
+        <v>32</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>63</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="26.4" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="39.6" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="76.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C21" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="E21" s="14" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="118.8" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
-        <v>41</v>
-      </c>
       <c r="B22" s="10" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -1385,10 +1425,12 @@
     <mergeCell ref="A4:M4"/>
     <mergeCell ref="A14:E14"/>
   </mergeCells>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
   <tableParts count="2">
-    <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
@@ -1399,100 +1441,101 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="56.6640625" customWidth="1"/>
-    <col min="2" max="2" width="38.44140625" customWidth="1"/>
-    <col min="3" max="4" width="43.88671875" customWidth="1"/>
-    <col min="5" max="13" width="10.109375" customWidth="1"/>
+    <col min="1" max="1" width="56.7109375" customWidth="1"/>
+    <col min="2" max="2" width="38.42578125" customWidth="1"/>
+    <col min="3" max="4" width="43.85546875" customWidth="1"/>
+    <col min="5" max="13" width="10.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/season2026/tpbl_summary.xlsx
+++ b/data/season2026/tpbl_summary.xlsx
@@ -382,7 +382,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -433,6 +433,11 @@
       <sz val="10.0"/>
       <color rgb="FF181C1F"/>
       <name val="Roboto"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -531,7 +536,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -564,6 +569,9 @@
     </xf>
     <xf borderId="6" fillId="0" fontId="9" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="6" fillId="4" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" wrapText="1"/>
@@ -864,14 +872,15 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="24.25"/>
     <col customWidth="1" min="2" max="2" width="6.75"/>
-    <col customWidth="1" min="3" max="4" width="33.0"/>
-    <col customWidth="1" min="5" max="5" width="40.13"/>
+    <col customWidth="1" min="3" max="3" width="33.0"/>
+    <col customWidth="1" min="4" max="4" width="12.0"/>
+    <col customWidth="1" min="5" max="5" width="10.13"/>
     <col customWidth="1" min="6" max="6" width="9.13"/>
     <col customWidth="1" min="7" max="7" width="10.63"/>
     <col customWidth="1" min="8" max="8" width="23.88"/>
     <col customWidth="1" min="9" max="9" width="24.75"/>
     <col customWidth="1" min="10" max="10" width="21.5"/>
-    <col customWidth="1" min="11" max="11" width="16.0"/>
+    <col customWidth="1" min="11" max="11" width="18.38"/>
     <col customWidth="1" min="12" max="12" width="16.5"/>
     <col customWidth="1" min="13" max="13" width="18.63"/>
     <col customWidth="1" min="14" max="26" width="11.13"/>
@@ -1001,8 +1010,8 @@
       <c r="J6" s="15">
         <v>223.8</v>
       </c>
-      <c r="K6" s="15">
-        <v>111.9</v>
+      <c r="K6" s="14">
+        <v>106.4</v>
       </c>
       <c r="L6" s="15">
         <v>98.7</v>
@@ -1042,8 +1051,8 @@
       <c r="J7" s="15">
         <v>205.5</v>
       </c>
-      <c r="K7" s="15">
-        <v>102.8</v>
+      <c r="K7" s="14">
+        <v>97.7</v>
       </c>
       <c r="L7" s="15">
         <v>98.3</v>
@@ -1083,8 +1092,8 @@
       <c r="J8" s="15">
         <v>237.5</v>
       </c>
-      <c r="K8" s="15">
-        <v>118.7</v>
+      <c r="K8" s="14">
+        <v>107.5</v>
       </c>
       <c r="L8" s="15">
         <v>103.6</v>
@@ -1124,7 +1133,7 @@
       <c r="J9" s="15">
         <v>92.4</v>
       </c>
-      <c r="K9" s="15">
+      <c r="K9" s="14">
         <v>92.4</v>
       </c>
       <c r="L9" s="15">
@@ -1165,7 +1174,7 @@
       <c r="J10" s="15">
         <v>0.0</v>
       </c>
-      <c r="K10" s="15">
+      <c r="K10" s="17">
         <v>0.0</v>
       </c>
       <c r="L10" s="15">
@@ -1247,8 +1256,8 @@
       <c r="J12" s="15">
         <v>126.3</v>
       </c>
-      <c r="K12" s="15">
-        <v>126.3</v>
+      <c r="K12" s="14">
+        <v>104.5</v>
       </c>
       <c r="L12" s="15">
         <v>102.2</v>
@@ -1274,13 +1283,13 @@
       <c r="B15" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="D15" s="17" t="s">
+      <c r="D15" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="E15" s="17" t="s">
+      <c r="E15" s="18" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1291,13 +1300,13 @@
       <c r="B16" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="E16" s="18" t="s">
+      <c r="E16" s="19" t="s">
         <v>78</v>
       </c>
     </row>
@@ -1305,16 +1314,16 @@
       <c r="A17" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="C17" s="18" t="s">
+      <c r="C17" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="D17" s="18" t="s">
+      <c r="D17" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="E17" s="18" t="s">
+      <c r="E17" s="19" t="s">
         <v>82</v>
       </c>
     </row>
@@ -1325,13 +1334,13 @@
       <c r="B18" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="D18" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="E18" s="18" t="s">
+      <c r="E18" s="19" t="s">
         <v>85</v>
       </c>
     </row>
@@ -1339,16 +1348,16 @@
       <c r="A19" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="C19" s="19" t="s">
+      <c r="C19" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="D19" s="19" t="s">
+      <c r="D19" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="E19" s="18" t="s">
+      <c r="E19" s="19" t="s">
         <v>89</v>
       </c>
     </row>
@@ -1359,13 +1368,13 @@
       <c r="B20" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="D20" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="E20" s="18" t="s">
+      <c r="E20" s="19" t="s">
         <v>92</v>
       </c>
     </row>
@@ -1376,13 +1385,13 @@
       <c r="B21" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="C21" s="18" t="s">
+      <c r="C21" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="D21" s="18" t="s">
+      <c r="D21" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="E21" s="18" t="s">
+      <c r="E21" s="19" t="s">
         <v>92</v>
       </c>
     </row>
@@ -1393,13 +1402,13 @@
       <c r="B22" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="C22" s="18" t="s">
+      <c r="C22" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="D22" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="E22" s="18" t="s">
+      <c r="E22" s="19" t="s">
         <v>95</v>
       </c>
     </row>
